--- a/artfynd/A 49128-2025 artfynd.xlsx
+++ b/artfynd/A 49128-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129078335</v>
       </c>
       <c r="B2" t="n">
-        <v>91293</v>
+        <v>91296</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 49128-2025 artfynd.xlsx
+++ b/artfynd/A 49128-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129078335</v>
       </c>
       <c r="B2" t="n">
-        <v>91296</v>
+        <v>91299</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 49128-2025 artfynd.xlsx
+++ b/artfynd/A 49128-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129078335</v>
       </c>
       <c r="B2" t="n">
-        <v>91299</v>
+        <v>91305</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 49128-2025 artfynd.xlsx
+++ b/artfynd/A 49128-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129078335</v>
       </c>
       <c r="B2" t="n">
-        <v>91305</v>
+        <v>91312</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 49128-2025 artfynd.xlsx
+++ b/artfynd/A 49128-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129078335</v>
       </c>
       <c r="B2" t="n">
-        <v>91312</v>
+        <v>91314</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 49128-2025 artfynd.xlsx
+++ b/artfynd/A 49128-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129078335</v>
       </c>
       <c r="B2" t="n">
-        <v>91314</v>
+        <v>91313</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 49128-2025 artfynd.xlsx
+++ b/artfynd/A 49128-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129078335</v>
       </c>
       <c r="B2" t="n">
-        <v>91313</v>
+        <v>91316</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 49128-2025 artfynd.xlsx
+++ b/artfynd/A 49128-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129078335</v>
       </c>
       <c r="B2" t="n">
-        <v>91316</v>
+        <v>91318</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 49128-2025 artfynd.xlsx
+++ b/artfynd/A 49128-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129078335</v>
       </c>
       <c r="B2" t="n">
-        <v>91318</v>
+        <v>91322</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 49128-2025 artfynd.xlsx
+++ b/artfynd/A 49128-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129078335</v>
       </c>
       <c r="B2" t="n">
-        <v>91322</v>
+        <v>91323</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 49128-2025 artfynd.xlsx
+++ b/artfynd/A 49128-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129078335</v>
       </c>
       <c r="B2" t="n">
-        <v>91323</v>
+        <v>91326</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
